--- a/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTech_LNG_Imports.xlsx
+++ b/TIMES-NZ/v303/SubRES_TMPL/SubRES_NewTech_LNG_Imports.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -552,238 +552,175 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PRE, DISCINV</t>
+          <t>PRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LNGPORTSML</t>
+          <t>LNGPORTSTD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SmallScalePort</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PRE, DISCINV</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>LNGPORTSTD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>StandardPort</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>LNGCommodityCosts</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Defines costs for LNG import (Just the commodity, not infrastructure or delivery)</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>LNGCommodityCosts</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>Defines costs for LNG import (Just the commodity, not infrastructure or delivery)</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>~FI_T</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>~FI_T</t>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Comm-IN</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Comm-OUT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>COST</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TechName</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Comm-IN</t>
+          <t>IMPLNG</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Comm-OUT</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IMPLNG</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
           <t>LNG</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D15" t="n">
         <v>18</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>LNGImportConfigurations</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>Defines parameters for different LNG configurations</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>LNGImportConfigurations</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>Defines parameters for different LNG configurations. These are integers, calling MIP.</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>~FI_T</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>~FI_T</t>
+          <t>TechName</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Comm-IN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Comm-OUT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>INVCOST</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CAP2ACT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Eff</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>AFA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AFA~LO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FIXOM</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TechName</t>
+          <t>LNGPORTSTD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Comm-IN</t>
+          <t>LNG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Comm-OUT</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>INVCOST</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CAP2ACT</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Eff</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>AFA</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>AFA~LO</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>FIXOM</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>FLO_DELIV</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>LNGPORTSML</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LNG</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
           <t>NGA</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>295</v>
-      </c>
-      <c r="E21" t="n">
-        <v>9</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="D20" t="n">
+        <v>800</v>
+      </c>
+      <c r="E20" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G20" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>10</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>LNGPORTSTD</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LNG</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NGA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>800</v>
-      </c>
-      <c r="E22" t="n">
-        <v>40</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="H20" t="n">
         <v>0</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I20" t="n">
         <v>90</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
